--- a/utils/monday_sprint_sprint_2025-11.xlsx
+++ b/utils/monday_sprint_sprint_2025-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="199">
   <si>
     <t>Ticket</t>
   </si>
@@ -135,6 +135,9 @@
     <t>10/02/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -228,7 +231,7 @@
     <t>30/04/2025</t>
   </si>
   <si>
-    <t>02/03/2026</t>
+    <t>25/02/2026</t>
   </si>
   <si>
     <t>Semana 5</t>
@@ -366,7 +369,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -1335,21 +1338,21 @@
         <v>39</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1361,10 +1364,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>24</v>
@@ -1393,7 +1396,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
@@ -1405,10 +1408,10 @@
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>24</v>
@@ -1437,7 +1440,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1449,10 +1452,10 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>24</v>
@@ -1481,7 +1484,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -1493,22 +1496,22 @@
         <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>17</v>
@@ -1517,15 +1520,15 @@
         <v>25</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -1537,10 +1540,10 @@
         <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>24</v>
@@ -1569,7 +1572,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1581,10 +1584,10 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>24</v>
@@ -1613,7 +1616,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -1625,10 +1628,10 @@
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>24</v>
@@ -1657,7 +1660,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -1669,10 +1672,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>24</v>
@@ -1701,7 +1704,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -1713,10 +1716,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>24</v>
@@ -1745,7 +1748,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -1757,10 +1760,10 @@
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>24</v>
@@ -1789,7 +1792,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -1801,10 +1804,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>24</v>
@@ -1833,7 +1836,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1845,39 +1848,39 @@
         <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -1889,10 +1892,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>24</v>
@@ -1921,7 +1924,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -1933,10 +1936,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>24</v>
@@ -1965,7 +1968,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -1977,10 +1980,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -2009,7 +2012,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2021,10 +2024,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>24</v>
@@ -2053,7 +2056,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2065,10 +2068,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>24</v>
@@ -2097,7 +2100,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2109,10 +2112,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>24</v>
@@ -2133,7 +2136,7 @@
         <v>25</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>17</v>
@@ -2141,7 +2144,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2153,10 +2156,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>24</v>
@@ -2185,7 +2188,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2197,10 +2200,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>24</v>
@@ -2229,7 +2232,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2241,10 +2244,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>24</v>
@@ -2273,7 +2276,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2285,10 +2288,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>24</v>
@@ -2317,7 +2320,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2329,10 +2332,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>24</v>
@@ -2361,7 +2364,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2373,10 +2376,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>24</v>
@@ -2405,7 +2408,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2417,10 +2420,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>24</v>
@@ -2449,7 +2452,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2461,10 +2464,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>24</v>
@@ -2493,7 +2496,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2505,10 +2508,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>24</v>
@@ -2537,7 +2540,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2549,10 +2552,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2581,7 +2584,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2593,10 +2596,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2625,7 +2628,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2637,10 +2640,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>24</v>
@@ -2669,7 +2672,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2681,10 +2684,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2705,7 +2708,7 @@
         <v>25</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>17</v>
@@ -2713,7 +2716,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2725,10 +2728,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>24</v>
@@ -2757,7 +2760,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2769,10 +2772,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>24</v>
@@ -2801,7 +2804,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2813,39 +2816,39 @@
         <v>34</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2857,10 +2860,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>24</v>
@@ -2889,7 +2892,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2901,10 +2904,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>24</v>
@@ -2933,7 +2936,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -2945,10 +2948,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>24</v>
@@ -2977,7 +2980,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -2989,10 +2992,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>24</v>
@@ -3021,7 +3024,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3033,10 +3036,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>24</v>
@@ -3065,7 +3068,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3077,10 +3080,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3109,7 +3112,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3121,10 +3124,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3153,7 +3156,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3165,10 +3168,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>24</v>
@@ -3197,7 +3200,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3209,10 +3212,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>24</v>
@@ -3241,7 +3244,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3253,10 +3256,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>24</v>
@@ -3285,7 +3288,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3297,10 +3300,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>24</v>
@@ -3329,7 +3332,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3341,10 +3344,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>24</v>
@@ -3373,7 +3376,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3385,10 +3388,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>24</v>
@@ -3417,7 +3420,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3429,10 +3432,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>24</v>
@@ -3461,7 +3464,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3473,10 +3476,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>24</v>
@@ -3505,7 +3508,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3517,10 +3520,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>24</v>
@@ -3549,7 +3552,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3561,10 +3564,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>24</v>
@@ -3593,7 +3596,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3605,10 +3608,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>24</v>
@@ -3637,7 +3640,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3649,10 +3652,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>24</v>
@@ -3681,7 +3684,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3693,10 +3696,10 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>24</v>
@@ -3725,7 +3728,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3737,10 +3740,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>24</v>
@@ -3769,7 +3772,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3781,10 +3784,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>24</v>
@@ -3813,7 +3816,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -3825,10 +3828,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>24</v>
@@ -3857,7 +3860,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -3869,10 +3872,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>24</v>
@@ -3901,7 +3904,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -3913,39 +3916,39 @@
         <v>34</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -3957,10 +3960,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>24</v>
@@ -3989,7 +3992,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4001,39 +4004,39 @@
         <v>34</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4045,39 +4048,39 @@
         <v>34</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4089,39 +4092,39 @@
         <v>34</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4133,39 +4136,39 @@
         <v>34</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>38</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4177,10 +4180,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>24</v>
@@ -4201,7 +4204,7 @@
         <v>25</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>17</v>
@@ -4209,22 +4212,22 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>24</v>
@@ -4245,7 +4248,7 @@
         <v>25</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>17</v>
@@ -4264,23 +4267,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4288,16 +4291,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4316,7 +4319,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -4337,7 +4340,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4368,12 +4371,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B2">
         <v>72</v>
@@ -4397,25 +4400,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4432,13 +4435,13 @@
         <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4450,10 +4453,10 @@
         <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -4470,27 +4473,27 @@
         <v>9</v>
       </c>
       <c r="J11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K11">
         <v>72</v>
       </c>
       <c r="M11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4502,7 +4505,7 @@
         <v>63</v>
       </c>
       <c r="M12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4511,32 +4514,32 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q13">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4548,7 +4551,7 @@
         <v>4</v>
       </c>
       <c r="P14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="Q14">
         <v>2</v>
@@ -4556,7 +4559,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4564,7 +4567,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4572,7 +4575,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4580,7 +4583,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -4591,7 +4594,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4599,128 +4602,128 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-11.xlsx
+++ b/utils/monday_sprint_sprint_2025-11.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="236">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>26568</t>
+    <t>9180073275</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>19/05/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>29/05/2025</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -102,7 +102,7 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>31582</t>
+    <t>9170156672</t>
   </si>
   <si>
     <t>MPO Ajustagem</t>
@@ -114,22 +114,31 @@
     <t>16/05/2025</t>
   </si>
   <si>
+    <t>21/05/2025</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
-    <t>31631</t>
+    <t>9169985914</t>
   </si>
   <si>
     <t>Alteração Sistema de Embalagem</t>
   </si>
   <si>
-    <t>31568</t>
+    <t>26/05/2025</t>
+  </si>
+  <si>
+    <t>9170238135</t>
   </si>
   <si>
     <t>Administrar os tipos de pré-listas</t>
   </si>
   <si>
-    <t>31699</t>
+    <t>20/05/2025</t>
+  </si>
+  <si>
+    <t>9171019561</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -141,6 +150,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -159,24 +171,33 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>9170803464</t>
   </si>
   <si>
     <t>Extrair planilha</t>
   </si>
   <si>
+    <t>9170792260</t>
+  </si>
+  <si>
     <t>Visualizar faseamento.</t>
   </si>
   <si>
-    <t>31554</t>
+    <t>9170261498</t>
   </si>
   <si>
     <t>FORMULÁRIO DE EMBALAGEM</t>
   </si>
   <si>
+    <t>31/05/2025</t>
+  </si>
+  <si>
     <t>30069</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Sistema de Controle de Importação - Criação da estrutura (copy)</t>
   </si>
   <si>
@@ -189,46 +210,52 @@
     <t>ADH</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9180309009</t>
   </si>
   <si>
     <t>Atualizar retroativamente o número da proforma no Benner para documentos integrados a partir 01/01/2025 (copy) (copy)</t>
   </si>
   <si>
+    <t>9170814357</t>
+  </si>
+  <si>
     <t>Novo item / Ajuste</t>
   </si>
   <si>
-    <t>31413</t>
+    <t>9170593000</t>
   </si>
   <si>
     <t>Registro de magnetismo residual</t>
   </si>
   <si>
-    <t>31530</t>
+    <t>9170287903</t>
   </si>
   <si>
     <t>Solicitação de Transferência de material</t>
   </si>
   <si>
-    <t>31620</t>
+    <t>9180817760</t>
   </si>
   <si>
     <t>Qlik - Saldo do Estoque Físico - Data warehouse</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>22/05/2025</t>
+  </si>
+  <si>
+    <t>9180288412</t>
   </si>
   <si>
     <t>Sistema gestão de ações - Homologação</t>
   </si>
   <si>
-    <t>31416</t>
+    <t>9170580548</t>
   </si>
   <si>
     <t>Gráfico para análise do indicador perfomance</t>
   </si>
   <si>
-    <t>31398</t>
+    <t>9057815229</t>
   </si>
   <si>
     <t>CONSULTA DE SEQ DE PRÉ-PRODUTIVO NO SISTEMA</t>
@@ -240,94 +267,112 @@
     <t>Semana 1</t>
   </si>
   <si>
+    <t>9180309135</t>
+  </si>
+  <si>
     <t>Enviar PROFORMA para o Benner ao enviar NF e parcelas. Informação será usada para o controle e baixa de adiantamentos</t>
   </si>
   <si>
-    <t>31682</t>
+    <t>9171198334</t>
   </si>
   <si>
     <t>Revisão de Pontos</t>
   </si>
   <si>
-    <t>31702</t>
+    <t>9171537040</t>
   </si>
   <si>
     <t>Log de acesso por usuário</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9180281818</t>
   </si>
   <si>
     <t>Criação de Sistema de Controle impostos e declarações</t>
   </si>
   <si>
-    <t>31681</t>
+    <t>01/06/2025</t>
+  </si>
+  <si>
+    <t>9171212440</t>
   </si>
   <si>
     <t>Horímetro jato gancheira</t>
   </si>
   <si>
-    <t>31289</t>
+    <t>28/05/2025</t>
+  </si>
+  <si>
+    <t>9058069720</t>
   </si>
   <si>
     <t>TEMPOS DO ROTEIRO PRELIMINAR</t>
   </si>
   <si>
-    <t>31700</t>
+    <t>9171336887</t>
   </si>
   <si>
     <t>IA para programação automática de máquinas de usinagem</t>
   </si>
   <si>
+    <t>9180309244</t>
+  </si>
+  <si>
     <t>Ao emitir a NF de exportação, dividir as parcelas conforme cadastro da proforma (CPC355A % parcelas ) ao invés de seguir a OTF (copy)</t>
   </si>
   <si>
-    <t>31542</t>
+    <t>9170272512</t>
   </si>
   <si>
     <t>E-mail da Liberação de Embarque com pendencia</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9180328452</t>
   </si>
   <si>
     <t>Revisar os campos necessários ao criar uma ordem de coleta</t>
   </si>
   <si>
+    <t>9170783765</t>
+  </si>
+  <si>
     <t>Cadastro de cotações</t>
   </si>
   <si>
-    <t>31516</t>
+    <t>9170486124</t>
   </si>
   <si>
     <t>Codificação do sistema de impressão de código de barras dos materiais</t>
   </si>
   <si>
-    <t>31701</t>
+    <t>9171325337</t>
   </si>
   <si>
     <t>IA para a predição e dimensionamento de estoque</t>
   </si>
   <si>
-    <t>31524</t>
+    <t>9170467329</t>
   </si>
   <si>
     <t>Add Filtro - IROG Usinagem</t>
   </si>
   <si>
-    <t>31673</t>
+    <t>9169608559</t>
   </si>
   <si>
     <t>Sistemas de investimentos</t>
   </si>
   <si>
-    <t>31292</t>
+    <t>27/05/2025</t>
+  </si>
+  <si>
+    <t>9171589480</t>
   </si>
   <si>
     <t>Apontamento eletrônico corte pó de ferro - Tela de Apontamento</t>
   </si>
   <si>
-    <t>31520</t>
+    <t>9170477958</t>
   </si>
   <si>
     <t>Sistema tablet acabamento linhas UPR</t>
@@ -339,6 +384,9 @@
     <t>Rever rotinas de geração do planilhão para otimização de tempo</t>
   </si>
   <si>
+    <t>9280042651</t>
+  </si>
+  <si>
     <t>Apontamento eletrônico corte pó de ferro - Tela de Apontamento (copy)</t>
   </si>
   <si>
@@ -348,16 +396,19 @@
     <t>Junho</t>
   </si>
   <si>
-    <t>31022</t>
+    <t>9180362705</t>
   </si>
   <si>
     <t>QlikSense Controle de Investimentos Dashboard</t>
   </si>
   <si>
+    <t>9180309346</t>
+  </si>
+  <si>
     <t>Enviar cotação da moeda para o Benner ao faturar e integrar a NF. A partir dessa informação a variação cambial será gerada e controlada automaticamente pelo Benner (verificar layout de integração já usado no passado) (copy) (copy)</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>9141463692</t>
   </si>
   <si>
     <t>Registro de Pintura - Reunião</t>
@@ -369,139 +420,193 @@
     <t>Semana 2</t>
   </si>
   <si>
-    <t>29095</t>
+    <t>9180440311</t>
   </si>
   <si>
     <t>Diário do bordo Ajustagem - Criação diário  de bordo</t>
   </si>
   <si>
-    <t>31464</t>
+    <t>9170555963</t>
   </si>
   <si>
     <t>Padronizar aplicações do IROG</t>
   </si>
   <si>
-    <t>31113</t>
+    <t>9180513304</t>
   </si>
   <si>
     <t>Implementar regra para novas contas PPR para diretoria industrial</t>
   </si>
   <si>
-    <t>31445</t>
+    <t>9170562537</t>
   </si>
   <si>
     <t>Alteração do Cálculo de Razão Critica para Referência por Data de Tratamento Térmico e Depósito</t>
   </si>
   <si>
-    <t>31509</t>
+    <t>9170539546</t>
   </si>
   <si>
     <t>ELIMINAR CÓDIGO DE ANEXO EM CPPs TIPO DE PRODUÇÃO NORMAL</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>9180749364</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber) Validação</t>
   </si>
   <si>
-    <t>31011</t>
+    <t>9180440553</t>
   </si>
   <si>
     <t>Homologação Refugo Fast LOOP e Carrossel</t>
   </si>
   <si>
-    <t>31510</t>
+    <t>9170533465</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DE FLUXOS 107, 110 E 111</t>
   </si>
   <si>
-    <t>31670</t>
+    <t>9169623180</t>
   </si>
   <si>
     <t>Cartão de Credito - vencimento 15/05/2025</t>
   </si>
   <si>
-    <t>31637</t>
+    <t>9169737887</t>
   </si>
   <si>
     <t>Incluir coluna Planilha do MPS</t>
   </si>
   <si>
-    <t>31651</t>
+    <t>9169654353</t>
   </si>
   <si>
     <t>Incluir pergunta na MPO Usinagem</t>
   </si>
   <si>
-    <t>31647</t>
+    <t>9169705221</t>
   </si>
   <si>
     <t>Relatório - 2ª corda</t>
   </si>
   <si>
+    <t>9170100940</t>
+  </si>
+  <si>
     <t>Qlik - Saldo do Estoque Físico</t>
   </si>
   <si>
-    <t>31639</t>
+    <t>9169719156</t>
   </si>
   <si>
     <t>MPO - Pintura/Embalagem e Ajustagem</t>
   </si>
   <si>
+    <t>9189850715</t>
+  </si>
+  <si>
     <t>No agendamento, colocar um combo box com os tipos de veículos</t>
   </si>
   <si>
-    <t>20/05/2025</t>
+    <t>9189851569</t>
   </si>
   <si>
     <t>Adicionar filtro de data com a opção "até" uma data específica</t>
   </si>
   <si>
+    <t>9189853736</t>
+  </si>
+  <si>
     <t>Tornar visível o código do agendamento na tela de visão master</t>
   </si>
   <si>
+    <t>9189855287</t>
+  </si>
+  <si>
     <t>Tirar o filtro de OC e colocar pelo nome do fornecedor</t>
   </si>
   <si>
+    <t>23/05/2025</t>
+  </si>
+  <si>
+    <t>9189857658</t>
+  </si>
+  <si>
     <t>No lugar da transportadore, colocar o CNPJ da transportadora</t>
   </si>
   <si>
+    <t>25/05/2025</t>
+  </si>
+  <si>
+    <t>9189858525</t>
+  </si>
+  <si>
     <t>Alterar a cor do alerta ao agendar para verde</t>
   </si>
   <si>
+    <t>9189859542</t>
+  </si>
+  <si>
     <t>Fechar a janela de agendamento do confirmar a agenda</t>
   </si>
   <si>
+    <t>9189863890</t>
+  </si>
+  <si>
     <t>Ao dar entrada na empresa, criar um status "Aguardando (no pátio)</t>
   </si>
   <si>
+    <t>9189865563</t>
+  </si>
+  <si>
     <t>Trocar "Volume de entrega" para "Quantidade de volumes"</t>
   </si>
   <si>
+    <t>9189866283</t>
+  </si>
+  <si>
     <t>Verificar uma rotina de envio de email, e nesse email enviar informações pertinentes do agendamento, com o código do agendamento.</t>
   </si>
   <si>
+    <t>9189901497</t>
+  </si>
+  <si>
     <t>Criação da tabela de cadastro e log</t>
   </si>
   <si>
+    <t>9191769695</t>
+  </si>
+  <si>
     <t>Criar um campo no agendamento para informar o número do CTE</t>
   </si>
   <si>
+    <t>9189902394</t>
+  </si>
+  <si>
     <t>Cadastro das sequências</t>
   </si>
   <si>
+    <t>9189903313</t>
+  </si>
+  <si>
     <t>Cadastro FUNDO / PRIMER</t>
   </si>
   <si>
+    <t>9189904212</t>
+  </si>
+  <si>
     <t>Cadastro ACABAMENTO / TOP COAT</t>
   </si>
   <si>
+    <t>9189905184</t>
+  </si>
+  <si>
     <t>Extração da planilha</t>
   </si>
   <si>
-    <t>32005</t>
+    <t>9266756304</t>
   </si>
   <si>
     <t>Coluna "Data MPS ToTo" no Arq ERP</t>
@@ -513,7 +618,7 @@
     <t>Semana 5</t>
   </si>
   <si>
-    <t>31928</t>
+    <t>9266779003</t>
   </si>
   <si>
     <t>Correção</t>
@@ -528,7 +633,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-11</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -589,6 +694,9 @@
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
   <si>
     <t>Baixa</t>
@@ -1173,10 +1281,10 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>26</v>
@@ -1190,7 +1298,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1202,10 +1310,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
@@ -1220,10 +1328,10 @@
         <v>32</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>26</v>
@@ -1237,7 +1345,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1249,10 +1357,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>31</v>
@@ -1267,10 +1375,10 @@
         <v>32</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
@@ -1284,22 +1392,22 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>31</v>
@@ -1317,7 +1425,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>26</v>
@@ -1331,40 +1439,40 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>26</v>
@@ -1378,7 +1486,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1390,10 +1498,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>31</v>
@@ -1408,10 +1516,10 @@
         <v>32</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>26</v>
@@ -1425,7 +1533,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1437,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>31</v>
@@ -1458,7 +1566,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
@@ -1472,7 +1580,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1484,10 +1592,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>31</v>
@@ -1502,10 +1610,10 @@
         <v>32</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>26</v>
@@ -1519,40 +1627,40 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
@@ -1566,7 +1674,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1578,10 +1686,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>31</v>
@@ -1596,10 +1704,10 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>26</v>
@@ -1613,7 +1721,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1625,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>31</v>
@@ -1643,10 +1751,10 @@
         <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>26</v>
@@ -1660,7 +1768,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1672,10 +1780,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>31</v>
@@ -1690,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1707,7 +1815,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1719,10 +1827,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>31</v>
@@ -1737,10 +1845,10 @@
         <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>26</v>
@@ -1754,7 +1862,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1766,10 +1874,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>31</v>
@@ -1784,10 +1892,10 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -1801,7 +1909,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1813,10 +1921,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>31</v>
@@ -1834,7 +1942,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
@@ -1848,7 +1956,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1860,10 +1968,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>31</v>
@@ -1878,10 +1986,10 @@
         <v>32</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1895,7 +2003,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1907,10 +2015,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>31</v>
@@ -1922,19 +2030,19 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>28</v>
@@ -1942,7 +2050,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1954,10 +2062,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>31</v>
@@ -1972,10 +2080,10 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>26</v>
@@ -1989,7 +2097,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2001,10 +2109,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>31</v>
@@ -2019,10 +2127,10 @@
         <v>32</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2036,22 +2144,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2066,10 +2174,10 @@
         <v>32</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
@@ -2083,22 +2191,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>31</v>
@@ -2113,10 +2221,10 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>26</v>
@@ -2130,7 +2238,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -2142,10 +2250,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>31</v>
@@ -2160,10 +2268,10 @@
         <v>32</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
@@ -2177,7 +2285,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2189,10 +2297,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>31</v>
@@ -2204,19 +2312,19 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="O25" s="2" t="s">
         <v>28</v>
@@ -2224,22 +2332,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>31</v>
@@ -2257,7 +2365,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
@@ -2271,7 +2379,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>58</v>
+        <v>100</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2283,10 +2391,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>31</v>
@@ -2301,10 +2409,10 @@
         <v>23</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
@@ -2318,7 +2426,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2330,10 +2438,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>31</v>
@@ -2348,10 +2456,10 @@
         <v>32</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
@@ -2365,22 +2473,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>31</v>
@@ -2395,10 +2503,10 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>26</v>
@@ -2412,7 +2520,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2424,10 +2532,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>31</v>
@@ -2442,10 +2550,10 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
@@ -2459,7 +2567,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2471,10 +2579,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>31</v>
@@ -2489,10 +2597,10 @@
         <v>32</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
@@ -2506,22 +2614,22 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>31</v>
@@ -2539,7 +2647,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>26</v>
@@ -2553,7 +2661,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2565,10 +2673,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>31</v>
@@ -2583,10 +2691,10 @@
         <v>32</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
@@ -2600,7 +2708,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2612,10 +2720,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>31</v>
@@ -2630,10 +2738,10 @@
         <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M34" s="2" t="s">
         <v>26</v>
@@ -2647,7 +2755,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2659,10 +2767,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2677,10 +2785,10 @@
         <v>32</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2694,7 +2802,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2706,10 +2814,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2724,7 +2832,7 @@
         <v>32</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2741,7 +2849,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2753,10 +2861,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>107</v>
+        <v>122</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>31</v>
@@ -2771,10 +2879,10 @@
         <v>32</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M37" s="2" t="s">
         <v>26</v>
@@ -2788,7 +2896,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2800,10 +2908,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2815,42 +2923,42 @@
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="O38" s="2" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>31</v>
@@ -2882,7 +2990,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>58</v>
+        <v>129</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2894,10 +3002,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>31</v>
@@ -2912,10 +3020,10 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M40" s="2" t="s">
         <v>26</v>
@@ -2929,7 +3037,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2941,10 +3049,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>31</v>
@@ -2956,19 +3064,19 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -2976,22 +3084,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>31</v>
@@ -3006,10 +3114,10 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
@@ -3023,7 +3131,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3035,10 +3143,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>31</v>
@@ -3053,10 +3161,10 @@
         <v>32</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
@@ -3070,7 +3178,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3082,10 +3190,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>31</v>
@@ -3100,10 +3208,10 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>26</v>
@@ -3117,7 +3225,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3129,10 +3237,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>31</v>
@@ -3147,10 +3255,10 @@
         <v>32</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M45" s="2" t="s">
         <v>26</v>
@@ -3164,7 +3272,7 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -3176,10 +3284,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>31</v>
@@ -3194,10 +3302,10 @@
         <v>32</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M46" s="2" t="s">
         <v>26</v>
@@ -3211,7 +3319,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3223,10 +3331,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3244,7 +3352,7 @@
         <v>24</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>26</v>
@@ -3258,22 +3366,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3288,10 +3396,10 @@
         <v>23</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>26</v>
@@ -3305,7 +3413,7 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3317,10 +3425,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>31</v>
@@ -3335,10 +3443,10 @@
         <v>32</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
@@ -3352,7 +3460,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3364,10 +3472,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>31</v>
@@ -3382,10 +3490,10 @@
         <v>32</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M50" s="2" t="s">
         <v>26</v>
@@ -3399,7 +3507,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3411,10 +3519,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>31</v>
@@ -3429,10 +3537,10 @@
         <v>32</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>26</v>
@@ -3446,7 +3554,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3458,10 +3566,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>31</v>
@@ -3476,10 +3584,10 @@
         <v>32</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L52" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M52" s="2" t="s">
         <v>26</v>
@@ -3493,7 +3601,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3505,10 +3613,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>31</v>
@@ -3523,10 +3631,10 @@
         <v>32</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M53" s="2" t="s">
         <v>26</v>
@@ -3540,7 +3648,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>65</v>
+        <v>159</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3552,10 +3660,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>31</v>
@@ -3570,10 +3678,10 @@
         <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>26</v>
@@ -3587,7 +3695,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3599,10 +3707,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>31</v>
@@ -3617,10 +3725,10 @@
         <v>32</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>26</v>
@@ -3634,22 +3742,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>91</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>31</v>
@@ -3661,13 +3769,13 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M56" s="2" t="s">
         <v>26</v>
@@ -3681,22 +3789,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>91</v>
+        <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>31</v>
@@ -3708,13 +3816,13 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>26</v>
@@ -3728,22 +3836,22 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>91</v>
+        <v>167</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>31</v>
@@ -3755,13 +3863,13 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M58" s="2" t="s">
         <v>26</v>
@@ -3775,22 +3883,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>31</v>
@@ -3802,13 +3910,13 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>171</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>26</v>
@@ -3822,22 +3930,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>91</v>
+        <v>172</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>150</v>
+        <v>173</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>31</v>
@@ -3849,13 +3957,13 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M60" s="2" t="s">
         <v>26</v>
@@ -3869,22 +3977,22 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>31</v>
@@ -3896,13 +4004,13 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M61" s="2" t="s">
         <v>26</v>
@@ -3916,22 +4024,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>91</v>
+        <v>177</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>31</v>
@@ -3943,13 +4051,13 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
@@ -3963,22 +4071,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>91</v>
+        <v>179</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>153</v>
+        <v>180</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>31</v>
@@ -3990,13 +4098,13 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M63" s="2" t="s">
         <v>26</v>
@@ -4010,22 +4118,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>31</v>
@@ -4037,13 +4145,13 @@
         <v>22</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M64" s="2" t="s">
         <v>26</v>
@@ -4057,22 +4165,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>31</v>
@@ -4084,13 +4192,13 @@
         <v>22</v>
       </c>
       <c r="J65" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M65" s="2" t="s">
         <v>26</v>
@@ -4104,7 +4212,7 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
@@ -4116,10 +4224,10 @@
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>31</v>
@@ -4131,13 +4239,13 @@
         <v>22</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>26</v>
@@ -4151,22 +4259,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>91</v>
+        <v>187</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>31</v>
@@ -4178,13 +4286,13 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="L67" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M67" s="2" t="s">
         <v>26</v>
@@ -4198,7 +4306,7 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>114</v>
+        <v>189</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
@@ -4210,10 +4318,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>31</v>
@@ -4225,13 +4333,13 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
@@ -4245,7 +4353,7 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>114</v>
+        <v>191</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>16</v>
@@ -4257,10 +4365,10 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>159</v>
+        <v>192</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>31</v>
@@ -4272,13 +4380,13 @@
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M69" s="2" t="s">
         <v>26</v>
@@ -4292,7 +4400,7 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>114</v>
+        <v>193</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
@@ -4304,10 +4412,10 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>31</v>
@@ -4319,13 +4427,13 @@
         <v>22</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M70" s="2" t="s">
         <v>26</v>
@@ -4339,7 +4447,7 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>114</v>
+        <v>195</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
@@ -4351,10 +4459,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>31</v>
@@ -4366,13 +4474,13 @@
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>146</v>
+        <v>40</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
@@ -4386,7 +4494,7 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
@@ -4398,10 +4506,10 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>163</v>
+        <v>198</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>31</v>
@@ -4413,19 +4521,19 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M72" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>28</v>
@@ -4433,22 +4541,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>166</v>
+        <v>201</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>168</v>
+        <v>203</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>31</v>
@@ -4460,19 +4568,19 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>164</v>
+        <v>199</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M73" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
@@ -4491,23 +4599,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>169</v>
+        <v>204</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B2" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4515,16 +4623,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>176</v>
+        <v>211</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>177</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4535,20 +4643,20 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>366</v>
+        <v>13.67</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>178</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K22">
         <v>68</v>
@@ -4564,7 +4672,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>179</v>
+        <v>214</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -4595,12 +4703,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="B2">
         <v>72</v>
@@ -4614,35 +4722,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>366</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>181</v>
+        <v>216</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>182</v>
+        <v>217</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>183</v>
+        <v>218</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>185</v>
+        <v>220</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>186</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4650,7 +4758,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -4659,33 +4767,39 @@
         <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>188</v>
+        <v>223</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N10">
         <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="Q10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
       <c r="D11" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E11">
         <v>22</v>
@@ -4703,21 +4817,27 @@
         <v>72</v>
       </c>
       <c r="M11" t="s">
-        <v>189</v>
+        <v>224</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>117</v>
+        <v>27</v>
       </c>
       <c r="Q11">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>60</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>167</v>
+        <v>202</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4729,47 +4849,47 @@
         <v>63</v>
       </c>
       <c r="J12" t="s">
-        <v>190</v>
+        <v>225</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>191</v>
+        <v>226</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>227</v>
       </c>
       <c r="Q12">
-        <v>66</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G13" t="s">
-        <v>192</v>
+        <v>228</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>194</v>
+        <v>230</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -4783,7 +4903,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4791,7 +4911,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>196</v>
+        <v>232</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4799,7 +4919,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>197</v>
+        <v>233</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4807,10 +4927,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4818,7 +4938,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4826,142 +4946,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F21" s="2">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>90</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>183</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
